--- a/research/mebs-competitors/MEBS_Competitors_UAE_Security.xlsx
+++ b/research/mebs-competitors/MEBS_Competitors_UAE_Security.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded (gov-linked)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Security Only'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Security Only'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MEBS Facility Services: 20 private-sector competitors (UAE)</t>
+          <t>MEBS Facility Services: 60 private-sector competitors (UAE), 20 per category</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. FM Companies (8)  2. Security Only (6)  3. Cleaning Only (6)  4. MEBS benchmark  5. Excluded (gov-linked)
+          <t>1. FM Companies (20)  2. Security Only (20)  3. Cleaning Only (20)  4. MEBS benchmark  5. Excluded (gov-linked)
 Separate files are also provided per category.</t>
         </is>
       </c>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1267,8 +1267,1338 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Emirates Security Services (Emirates Guard Services)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Manned guarding</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Locally owned private company. Owner not published</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>5,001 to 10,000 (directory)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Calls itself the largest locally owned security company</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 360M to 1,000M</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Police Security Support Services; federal licences</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Large Abu Dhabi guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>naukrigulf.com (Emirates Security Services); kompass.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>United Security Group (USG)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Security guarding and mobile patrolling</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Rashed Bin Khalaf Al Otaiba (per Naukri; another directory names different owners)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi (5 branches)</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>501 to 10,000 (sources conflict)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Five branch offices</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>US$10M to 50M (Naukri) vs US$172.6M (ZoomInfo), estimates</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 72M to 500M</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>One of the larger locally owned guarding firms</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Low to medium</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>naukrigulf.com (United Security Group); zoominfo.com; indeed.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Emirates Gateway Security Services (EGSS)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Manned guarding</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>166 to 500 (aggregator)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi guarding</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 12M to 50M</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>prospeo.io (EGSS); propertyfinder.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Al Falah Security Services</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Guarding, access control, perimeter patrols, electronic security operations, 24/7 operations centre</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Mussafah, Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>24/7 operations centre</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>naukrigulf.com (Al Falah Security Services)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>RANN Security Services</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Guarding, remote monitoring, risk assessments, virtual guarding, field supervision</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Al Rigga, Dubai</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Claims to be a large SIRA-certified firm</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>ISO 9001:2008 (per listing)</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Dubai guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>bayut.com (security companies); hidubai.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Black Horse Security Services</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Guarding and patrol for events, retail and residential</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Wael Ahmed (per Prospeo, unverified)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Port Saeed, Dubai</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>21 to 50 (aggregator)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Events, hospitals, hotels</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 2M to 5M</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Events, hospitals, hotels</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Small Dubai guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>sothebysrealty.ae (security companies); hidubai.com; prospeo.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Doorsec Security Services LLC</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Manned guarding</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>42 to 100 (aggregator)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Hires directly</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 3M to 10M</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Not confirmed</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>Dubai guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>prospeo.io (Doorsec); ae.indeed.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Westminster Security UAE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Close protection, security advance teams, chauffeurs, counter-surveillance, residential security</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Westminster Security Group (UK, private; CEO John Moore)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>British (parent)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>High-net-worth and family office clients</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Private families and individuals</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Premium security competitor for VIP and residential work</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>westminstersecurity.co.uk (Dubai launch); securitysystemsnews.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Belhasa Falcon (formerly BELCOM)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Private security guarding</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Belhasa Group of Companies</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Emirati</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Private family group</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>1993 or 1995 (sources conflict)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Part of Belhasa Group</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>Emirati family-owned Dubai guarding firm</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>naukrigulf.com (Belhasa Falcon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Fursan Security Services LLC</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Manned guarding and mobile security</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>20 to 29 (aggregators)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Small guarding firm</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 1M to 3M</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>Small Abu Dhabi guarding competitor</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>village.ai (Fursan Security Services); aeroleads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Focus Security Services UAE</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Manned guarding</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>58 to 200 (aggregator)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Northern emirates guarding</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 4M to 20M</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Guarding competitor in the northern emirates</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>prospeo.io (Focus Security Services UAE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Hawk Security Services LLC</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Physical guarding, housekeeping, kitchen duct cleaning, office support</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Garhoud, Dubai</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>All emirates</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>1,200+ (company); 11 to 50 (ZoomInfo)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Security plus housekeeping, close to MEBS's mix</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 72M to 120M</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Bundles security and housekeeping like MEBS</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>naukrigulf.com (Hawk Security Services); kompass.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Severity Security &amp; Guarding Services LLC</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Manned guarding, hospitality security</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Private. Owner not published</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Hospitality-focused</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Cannot estimate (headcount unknown)</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>SIRA (per listings)</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>Dubai guarding competitor in hospitality</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>severitysecurity.ae; thetalentpoint.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Blue Diamond Facilities Management Services LLC</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>SIRA-approved guarding (part of Blue Diamond group, which also offers FM and cleaning)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Private (Blue Diamond Group). Owner not published</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2012 (group 1995)</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Business Bay, Dubai</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>27 to 100 (aggregator)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Guards trained at Dubai Police-approved institutes</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>approx. AED 2M to 10M</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>SIRA; ISO 9001, 14001, 45001</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>Dubai security firm in a group that also does FM and cleaning</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>No government or state shareholder found in public sources</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>dubizzle.com (security companies); prospeo.io; village.ai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1417,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1616,6 +2946,138 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Khadamat Facilities Management</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Set up as a JV of Mubadala (Abu Dhabi state investor) and Serco</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Ontegra (formerly Deyaar FM)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Subsidiary of Deyaar Development (government-linked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Tafawuq Facility Management</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Eltizam, which is 50% ADQ (Abu Dhabi state holding) and 50% IHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Emirates International Facility Management</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Subsidiary of Das Holding, reported to be owned by Sheikh Mansour bin Zayed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Operon Middle East</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Edgenta, part of UEM Group, which belongs to Malaysia's state fund Khazanah</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Spark Security Services</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Acquired by Aldar Properties in 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>World Security</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Owned by DP World (Dubai Government)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>GardaWorld UAE</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Operates in the UAE through a joint venture with Transguard</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Global Security Services Group (GSSG)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Describes itself as the armed security provider for the UAE government</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Duserve FM &amp; Building Cleaning</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Owned by Dubai World Central (Government of Dubai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Hitches &amp; Glitches</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Not separate: a subsidiary of Farnek, which is already listed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
